--- a/notebooks/outputs/building_sector_constraint_evaluation.xlsx
+++ b/notebooks/outputs/building_sector_constraint_evaluation.xlsx
@@ -2152,16 +2152,16 @@
         <v>11133175</v>
       </c>
       <c r="E48" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F48" t="n">
         <v>11133175</v>
       </c>
       <c r="G48" t="n">
-        <v>-10268553</v>
+        <v>-10268556</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.9223382368461827</v>
+        <v>-0.9223385063110927</v>
       </c>
       <c r="I48" t="n">
         <v>96</v>
@@ -2188,16 +2188,16 @@
         <v>17483766</v>
       </c>
       <c r="E49" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F49" t="n">
         <v>17483766</v>
       </c>
       <c r="G49" t="n">
-        <v>-15444975</v>
+        <v>-15444973</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8833894825634249</v>
+        <v>-0.8833893681715942</v>
       </c>
       <c r="I49" t="n">
         <v>96</v>
@@ -2224,16 +2224,16 @@
         <v>20440924</v>
       </c>
       <c r="E50" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F50" t="n">
         <v>20440924</v>
       </c>
       <c r="G50" t="n">
-        <v>-18527959</v>
+        <v>-18527957</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.9064149448430022</v>
+        <v>-0.9064148470000671</v>
       </c>
       <c r="I50" t="n">
         <v>96</v>
@@ -2368,16 +2368,16 @@
         <v>17642541</v>
       </c>
       <c r="E54" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F54" t="n">
         <v>17642541</v>
       </c>
       <c r="G54" t="n">
-        <v>-16274357</v>
+        <v>-16274358</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9224497196860701</v>
+        <v>-0.9224497763672478</v>
       </c>
       <c r="I54" t="n">
         <v>96</v>
@@ -2404,16 +2404,16 @@
         <v>11250885</v>
       </c>
       <c r="E55" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F55" t="n">
         <v>11250885</v>
       </c>
       <c r="G55" t="n">
-        <v>-10325744</v>
+        <v>-10325730</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.917771713069683</v>
+        <v>-0.9177704687231271</v>
       </c>
       <c r="I55" t="n">
         <v>96</v>
@@ -5392,16 +5392,16 @@
         <v>744753</v>
       </c>
       <c r="E138" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F138" t="n">
         <v>744753</v>
       </c>
       <c r="G138" t="n">
-        <v>119869</v>
+        <v>119866</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1609513489707326</v>
+        <v>0.1609473207895772</v>
       </c>
       <c r="I138" t="n">
         <v>96</v>
@@ -5428,16 +5428,16 @@
         <v>1310680</v>
       </c>
       <c r="E139" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F139" t="n">
         <v>1310680</v>
       </c>
       <c r="G139" t="n">
-        <v>728111</v>
+        <v>728113</v>
       </c>
       <c r="H139" t="n">
-        <v>0.5555215613269447</v>
+        <v>0.5555230872524186</v>
       </c>
       <c r="I139" t="n">
         <v>96</v>
@@ -5464,16 +5464,16 @@
         <v>1535401</v>
       </c>
       <c r="E140" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F140" t="n">
         <v>1535401</v>
       </c>
       <c r="G140" t="n">
-        <v>377564</v>
+        <v>377566</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2459057926886852</v>
+        <v>0.2459070952799953</v>
       </c>
       <c r="I140" t="n">
         <v>96</v>
@@ -5608,16 +5608,16 @@
         <v>1035131</v>
       </c>
       <c r="E144" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F144" t="n">
         <v>1035131</v>
       </c>
       <c r="G144" t="n">
-        <v>333053</v>
+        <v>333052</v>
       </c>
       <c r="H144" t="n">
-        <v>0.3217496143000258</v>
+        <v>0.3217486482387253</v>
       </c>
       <c r="I144" t="n">
         <v>96</v>
@@ -5644,16 +5644,16 @@
         <v>717248</v>
       </c>
       <c r="E145" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F145" t="n">
         <v>717248</v>
       </c>
       <c r="G145" t="n">
-        <v>207893</v>
+        <v>207907</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2898481417863835</v>
+        <v>0.2898676608369769</v>
       </c>
       <c r="I145" t="n">
         <v>96</v>
@@ -8632,16 +8632,16 @@
         <v>864619</v>
       </c>
       <c r="E228" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F228" t="n">
         <v>864619</v>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>3.46973638099556e-06</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
         <v>96</v>
@@ -8668,16 +8668,16 @@
         <v>2038793</v>
       </c>
       <c r="E229" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F229" t="n">
         <v>2038793</v>
       </c>
       <c r="G229" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>-9.809725656307432e-07</v>
+        <v>0</v>
       </c>
       <c r="I229" t="n">
         <v>96</v>
@@ -8704,16 +8704,16 @@
         <v>1912967</v>
       </c>
       <c r="E230" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F230" t="n">
         <v>1912967</v>
       </c>
       <c r="G230" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>-1.045496341546927e-06</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>96</v>
@@ -8848,16 +8848,16 @@
         <v>1294358</v>
       </c>
       <c r="E234" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F234" t="n">
         <v>1294358</v>
       </c>
       <c r="G234" t="n">
-        <v>73826</v>
+        <v>73825</v>
       </c>
       <c r="H234" t="n">
-        <v>0.05703677035256088</v>
+        <v>0.05703599776877803</v>
       </c>
       <c r="I234" t="n">
         <v>96</v>
@@ -8884,16 +8884,16 @@
         <v>768068</v>
       </c>
       <c r="E235" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F235" t="n">
         <v>768068</v>
       </c>
       <c r="G235" t="n">
-        <v>157073</v>
+        <v>157087</v>
       </c>
       <c r="H235" t="n">
-        <v>0.2045040282891619</v>
+        <v>0.2045222558419307</v>
       </c>
       <c r="I235" t="n">
         <v>96</v>
@@ -11872,16 +11872,16 @@
         <v>3877828</v>
       </c>
       <c r="E318" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F318" t="n">
         <v>3877828</v>
       </c>
       <c r="G318" t="n">
-        <v>-3013206</v>
+        <v>-3013209</v>
       </c>
       <c r="H318" t="n">
-        <v>-0.7770344636224196</v>
+        <v>-0.7770352372513686</v>
       </c>
       <c r="I318" t="n">
         <v>96</v>
@@ -11908,16 +11908,16 @@
         <v>4204538</v>
       </c>
       <c r="E319" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F319" t="n">
         <v>4204538</v>
       </c>
       <c r="G319" t="n">
-        <v>-2165747</v>
+        <v>-2165745</v>
       </c>
       <c r="H319" t="n">
-        <v>-0.5150974970377244</v>
+        <v>-0.5150970213612054</v>
       </c>
       <c r="I319" t="n">
         <v>96</v>
@@ -11944,16 +11944,16 @@
         <v>5486568</v>
       </c>
       <c r="E320" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F320" t="n">
         <v>5486568</v>
       </c>
       <c r="G320" t="n">
-        <v>-3573603</v>
+        <v>-3573601</v>
       </c>
       <c r="H320" t="n">
-        <v>-0.6513366826037698</v>
+        <v>-0.6513363180771659</v>
       </c>
       <c r="I320" t="n">
         <v>96</v>
@@ -12088,16 +12088,16 @@
         <v>4807293</v>
       </c>
       <c r="E324" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F324" t="n">
         <v>4807293</v>
       </c>
       <c r="G324" t="n">
-        <v>-3439109</v>
+        <v>-3439110</v>
       </c>
       <c r="H324" t="n">
-        <v>-0.7153940897715201</v>
+        <v>-0.7153942977887972</v>
       </c>
       <c r="I324" t="n">
         <v>96</v>
@@ -12124,16 +12124,16 @@
         <v>3256581</v>
       </c>
       <c r="E325" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F325" t="n">
         <v>3256581</v>
       </c>
       <c r="G325" t="n">
-        <v>-2331440</v>
+        <v>-2331426</v>
       </c>
       <c r="H325" t="n">
-        <v>-0.7159164780486037</v>
+        <v>-0.7159121790614144</v>
       </c>
       <c r="I325" t="n">
         <v>96</v>
@@ -15112,16 +15112,16 @@
         <v>1419101</v>
       </c>
       <c r="E408" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F408" t="n">
         <v>1419101</v>
       </c>
       <c r="G408" t="n">
-        <v>-554479</v>
+        <v>-554482</v>
       </c>
       <c r="H408" t="n">
-        <v>-0.3907255368011157</v>
+        <v>-0.3907276508155516</v>
       </c>
       <c r="I408" t="n">
         <v>96</v>
@@ -15148,16 +15148,16 @@
         <v>3118121</v>
       </c>
       <c r="E409" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F409" t="n">
         <v>3118121</v>
       </c>
       <c r="G409" t="n">
-        <v>-1079330</v>
+        <v>-1079328</v>
       </c>
       <c r="H409" t="n">
-        <v>-0.346147567717866</v>
+        <v>-0.3461469263059387</v>
       </c>
       <c r="I409" t="n">
         <v>96</v>
@@ -15184,16 +15184,16 @@
         <v>3422052</v>
       </c>
       <c r="E410" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F410" t="n">
         <v>3422052</v>
       </c>
       <c r="G410" t="n">
-        <v>-1509087</v>
+        <v>-1509085</v>
       </c>
       <c r="H410" t="n">
-        <v>-0.4409889154226762</v>
+        <v>-0.4409883309780214</v>
       </c>
       <c r="I410" t="n">
         <v>96</v>
@@ -15328,16 +15328,16 @@
         <v>2908144</v>
       </c>
       <c r="E414" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F414" t="n">
         <v>2908144</v>
       </c>
       <c r="G414" t="n">
-        <v>-1539960</v>
+        <v>-1539961</v>
       </c>
       <c r="H414" t="n">
-        <v>-0.5295336131910937</v>
+        <v>-0.5295339570530208</v>
       </c>
       <c r="I414" t="n">
         <v>96</v>
@@ -15364,16 +15364,16 @@
         <v>2099518</v>
       </c>
       <c r="E415" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F415" t="n">
         <v>2099518</v>
       </c>
       <c r="G415" t="n">
-        <v>-1174377</v>
+        <v>-1174363</v>
       </c>
       <c r="H415" t="n">
-        <v>-0.5593555282688694</v>
+        <v>-0.5593488600716926</v>
       </c>
       <c r="I415" t="n">
         <v>96</v>
@@ -18352,16 +18352,16 @@
         <v>485281</v>
       </c>
       <c r="E498" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F498" t="n">
         <v>485281</v>
       </c>
       <c r="G498" t="n">
-        <v>379341</v>
+        <v>379338</v>
       </c>
       <c r="H498" t="n">
-        <v>0.7816934930483576</v>
+        <v>0.7816873110630748</v>
       </c>
       <c r="I498" t="n">
         <v>96</v>
@@ -18388,16 +18388,16 @@
         <v>1116161</v>
       </c>
       <c r="E499" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F499" t="n">
         <v>1116161</v>
       </c>
       <c r="G499" t="n">
-        <v>922630</v>
+        <v>922632</v>
       </c>
       <c r="H499" t="n">
-        <v>0.8266101395766381</v>
+        <v>0.826611931432831</v>
       </c>
       <c r="I499" t="n">
         <v>96</v>
@@ -18424,16 +18424,16 @@
         <v>1180520</v>
       </c>
       <c r="E500" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F500" t="n">
         <v>1180520</v>
       </c>
       <c r="G500" t="n">
-        <v>732445</v>
+        <v>732447</v>
       </c>
       <c r="H500" t="n">
-        <v>0.6204426862738455</v>
+        <v>0.6204443804425168</v>
       </c>
       <c r="I500" t="n">
         <v>96</v>
@@ -18568,16 +18568,16 @@
         <v>890449</v>
       </c>
       <c r="E504" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F504" t="n">
         <v>890449</v>
       </c>
       <c r="G504" t="n">
-        <v>477735</v>
+        <v>477734</v>
       </c>
       <c r="H504" t="n">
-        <v>0.5365102324782217</v>
+        <v>0.5365091094492779</v>
       </c>
       <c r="I504" t="n">
         <v>96</v>
@@ -18604,16 +18604,16 @@
         <v>468689</v>
       </c>
       <c r="E505" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F505" t="n">
         <v>468689</v>
       </c>
       <c r="G505" t="n">
-        <v>456452</v>
+        <v>456466</v>
       </c>
       <c r="H505" t="n">
-        <v>0.9738910023491057</v>
+        <v>0.9739208729029271</v>
       </c>
       <c r="I505" t="n">
         <v>96</v>
@@ -21592,16 +21592,16 @@
         <v>1524991</v>
       </c>
       <c r="E588" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F588" t="n">
         <v>1524991</v>
       </c>
       <c r="G588" t="n">
-        <v>-660369</v>
+        <v>-660372</v>
       </c>
       <c r="H588" t="n">
-        <v>-0.4330314080542115</v>
+        <v>-0.4330333752789361</v>
       </c>
       <c r="I588" t="n">
         <v>96</v>
@@ -21628,16 +21628,16 @@
         <v>2911838</v>
       </c>
       <c r="E589" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F589" t="n">
         <v>2911838</v>
       </c>
       <c r="G589" t="n">
-        <v>-873047</v>
+        <v>-873045</v>
       </c>
       <c r="H589" t="n">
-        <v>-0.2998267760775153</v>
+        <v>-0.2998260892261176</v>
       </c>
       <c r="I589" t="n">
         <v>96</v>
@@ -21664,16 +21664,16 @@
         <v>3609799</v>
       </c>
       <c r="E590" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F590" t="n">
         <v>3609799</v>
       </c>
       <c r="G590" t="n">
-        <v>-1696834</v>
+        <v>-1696832</v>
       </c>
       <c r="H590" t="n">
-        <v>-0.4700632916126355</v>
+        <v>-0.4700627375651664</v>
       </c>
       <c r="I590" t="n">
         <v>96</v>
@@ -21808,16 +21808,16 @@
         <v>2909259</v>
       </c>
       <c r="E594" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F594" t="n">
         <v>2909259</v>
       </c>
       <c r="G594" t="n">
-        <v>-1541075</v>
+        <v>-1541076</v>
       </c>
       <c r="H594" t="n">
-        <v>-0.5297139237173452</v>
+        <v>-0.5297142674474841</v>
       </c>
       <c r="I594" t="n">
         <v>96</v>
@@ -21844,16 +21844,16 @@
         <v>1851958</v>
       </c>
       <c r="E595" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F595" t="n">
         <v>1851958</v>
       </c>
       <c r="G595" t="n">
-        <v>-926817</v>
+        <v>-926803</v>
       </c>
       <c r="H595" t="n">
-        <v>-0.5004524940630403</v>
+        <v>-0.5004449344963546</v>
       </c>
       <c r="I595" t="n">
         <v>96</v>
@@ -24832,16 +24832,16 @@
         <v>529374</v>
       </c>
       <c r="E678" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F678" t="n">
         <v>529374</v>
       </c>
       <c r="G678" t="n">
-        <v>335248</v>
+        <v>335245</v>
       </c>
       <c r="H678" t="n">
-        <v>0.6332913970085422</v>
+        <v>0.6332857299376244</v>
       </c>
       <c r="I678" t="n">
         <v>96</v>
@@ -24868,16 +24868,16 @@
         <v>1189024</v>
       </c>
       <c r="E679" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F679" t="n">
         <v>1189024</v>
       </c>
       <c r="G679" t="n">
-        <v>849767</v>
+        <v>849769</v>
       </c>
       <c r="H679" t="n">
-        <v>0.7146760704577872</v>
+        <v>0.7146777525096213</v>
       </c>
       <c r="I679" t="n">
         <v>96</v>
@@ -24904,16 +24904,16 @@
         <v>1549032</v>
       </c>
       <c r="E680" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F680" t="n">
         <v>1549032</v>
       </c>
       <c r="G680" t="n">
-        <v>363933</v>
+        <v>363935</v>
       </c>
       <c r="H680" t="n">
-        <v>0.2349422090699224</v>
+        <v>0.2349435001988339</v>
       </c>
       <c r="I680" t="n">
         <v>96</v>
@@ -25048,16 +25048,16 @@
         <v>1471186</v>
       </c>
       <c r="E684" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F684" t="n">
         <v>1471186</v>
       </c>
       <c r="G684" t="n">
-        <v>-103002</v>
+        <v>-103003</v>
       </c>
       <c r="H684" t="n">
-        <v>-0.07001290115593814</v>
+        <v>-0.07001358087964404</v>
       </c>
       <c r="I684" t="n">
         <v>96</v>
@@ -25084,16 +25084,16 @@
         <v>662805</v>
       </c>
       <c r="E685" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F685" t="n">
         <v>662805</v>
       </c>
       <c r="G685" t="n">
-        <v>262336</v>
+        <v>262350</v>
       </c>
       <c r="H685" t="n">
-        <v>0.3957966521073317</v>
+        <v>0.3958177744585512</v>
       </c>
       <c r="I685" t="n">
         <v>96</v>
@@ -28072,16 +28072,16 @@
         <v>348225</v>
       </c>
       <c r="E768" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F768" t="n">
         <v>348225</v>
       </c>
       <c r="G768" t="n">
-        <v>516397</v>
+        <v>516394</v>
       </c>
       <c r="H768" t="n">
-        <v>1.482940627467873</v>
+        <v>1.482932012348338</v>
       </c>
       <c r="I768" t="n">
         <v>96</v>
@@ -28108,16 +28108,16 @@
         <v>776138</v>
       </c>
       <c r="E769" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F769" t="n">
         <v>776138</v>
       </c>
       <c r="G769" t="n">
-        <v>1262653</v>
+        <v>1262655</v>
       </c>
       <c r="H769" t="n">
-        <v>1.626840845313591</v>
+        <v>1.626843422174922</v>
       </c>
       <c r="I769" t="n">
         <v>96</v>
@@ -28144,16 +28144,16 @@
         <v>980908</v>
       </c>
       <c r="E770" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F770" t="n">
         <v>980908</v>
       </c>
       <c r="G770" t="n">
-        <v>932057</v>
+        <v>932059</v>
       </c>
       <c r="H770" t="n">
-        <v>0.9501981837236519</v>
+        <v>0.95020022265085</v>
       </c>
       <c r="I770" t="n">
         <v>96</v>
@@ -28288,16 +28288,16 @@
         <v>958538</v>
       </c>
       <c r="E774" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F774" t="n">
         <v>958538</v>
       </c>
       <c r="G774" t="n">
-        <v>409646</v>
+        <v>409645</v>
       </c>
       <c r="H774" t="n">
-        <v>0.4273654252622223</v>
+        <v>0.4273643820067645</v>
       </c>
       <c r="I774" t="n">
         <v>96</v>
@@ -28324,16 +28324,16 @@
         <v>500863</v>
       </c>
       <c r="E775" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F775" t="n">
         <v>500863</v>
       </c>
       <c r="G775" t="n">
-        <v>424278</v>
+        <v>424292</v>
       </c>
       <c r="H775" t="n">
-        <v>0.8470939159011546</v>
+        <v>0.8471218676564251</v>
       </c>
       <c r="I775" t="n">
         <v>96</v>
@@ -31312,16 +31312,16 @@
         <v>1339003</v>
       </c>
       <c r="E858" t="n">
-        <v>864622</v>
+        <v>864619</v>
       </c>
       <c r="F858" t="n">
         <v>1339003</v>
       </c>
       <c r="G858" t="n">
-        <v>-474381</v>
+        <v>-474384</v>
       </c>
       <c r="H858" t="n">
-        <v>-0.354279265991189</v>
+        <v>-0.3542815064641379</v>
       </c>
       <c r="I858" t="n">
         <v>96</v>
@@ -31348,16 +31348,16 @@
         <v>818473</v>
       </c>
       <c r="E859" t="n">
-        <v>2038791</v>
+        <v>2038793</v>
       </c>
       <c r="F859" t="n">
         <v>818473</v>
       </c>
       <c r="G859" t="n">
-        <v>1220318</v>
+        <v>1220320</v>
       </c>
       <c r="H859" t="n">
-        <v>1.49096915842062</v>
+        <v>1.490971601995423</v>
       </c>
       <c r="I859" t="n">
         <v>96</v>
@@ -31384,16 +31384,16 @@
         <v>763677</v>
       </c>
       <c r="E860" t="n">
-        <v>1912965</v>
+        <v>1912967</v>
       </c>
       <c r="F860" t="n">
         <v>763677</v>
       </c>
       <c r="G860" t="n">
-        <v>1149288</v>
+        <v>1149290</v>
       </c>
       <c r="H860" t="n">
-        <v>1.504939915697343</v>
+        <v>1.504942534605599</v>
       </c>
       <c r="I860" t="n">
         <v>96</v>
@@ -31528,16 +31528,16 @@
         <v>1368183</v>
       </c>
       <c r="E864" t="n">
-        <v>1368184</v>
+        <v>1368183</v>
       </c>
       <c r="F864" t="n">
         <v>1368183</v>
       </c>
       <c r="G864" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H864" t="n">
-        <v>7.308963786277128e-07</v>
+        <v>0</v>
       </c>
       <c r="I864" t="n">
         <v>96</v>
@@ -31564,16 +31564,16 @@
         <v>925155</v>
       </c>
       <c r="E865" t="n">
-        <v>925141</v>
+        <v>925155</v>
       </c>
       <c r="F865" t="n">
         <v>925155</v>
       </c>
       <c r="G865" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="H865" t="n">
-        <v>-1.513259940226232e-05</v>
+        <v>0</v>
       </c>
       <c r="I865" t="n">
         <v>96</v>
@@ -32900,16 +32900,16 @@
         <v>17037388726.27777</v>
       </c>
       <c r="E902" t="n">
-        <v>17037388405.5772</v>
+        <v>17037388447.40661</v>
       </c>
       <c r="F902" t="n">
         <v>17037388726.27777</v>
       </c>
       <c r="G902" t="n">
-        <v>-320.7005710601807</v>
+        <v>-278.8711605072021</v>
       </c>
       <c r="H902" t="n">
-        <v>-1.88233406076804e-08</v>
+        <v>-1.636818675605391e-08</v>
       </c>
       <c r="I902" t="n">
         <v>2880</v>
@@ -32940,16 +32940,16 @@
         <v>19720127178.55555</v>
       </c>
       <c r="E903" t="n">
-        <v>19720127269.47092</v>
+        <v>19720127169.47928</v>
       </c>
       <c r="F903" t="n">
         <v>19720127178.55555</v>
       </c>
       <c r="G903" t="n">
-        <v>90.91536331176758</v>
+        <v>-9.076274871826172</v>
       </c>
       <c r="H903" t="n">
-        <v>4.610282808451283e-09</v>
+        <v>-4.602543781612155e-10</v>
       </c>
       <c r="I903" t="n">
         <v>2880</v>
@@ -33020,16 +33020,16 @@
         <v>10854992261.36111</v>
       </c>
       <c r="E905" t="n">
-        <v>10854992118.76052</v>
+        <v>10854992399.07086</v>
       </c>
       <c r="F905" t="n">
         <v>10854992261.36111</v>
       </c>
       <c r="G905" t="n">
-        <v>-142.6005878448486</v>
+        <v>137.7097492218018</v>
       </c>
       <c r="H905" t="n">
-        <v>-1.313686683614161e-08</v>
+        <v>1.268630560999905e-08</v>
       </c>
       <c r="I905" t="n">
         <v>2880</v>
@@ -33100,16 +33100,16 @@
         <v>2204916009.7266</v>
       </c>
       <c r="E907" t="n">
-        <v>2204916021.158096</v>
+        <v>2204916000.433649</v>
       </c>
       <c r="F907" t="n">
         <v>2204916009.7266</v>
       </c>
       <c r="G907" t="n">
-        <v>11.43149614334106</v>
+        <v>-9.292951107025146</v>
       </c>
       <c r="H907" t="n">
-        <v>5.184549476221782e-09</v>
+        <v>-4.214650837506247e-09</v>
       </c>
       <c r="I907" t="n">
         <v>1440</v>
@@ -33140,16 +33140,16 @@
         <v>10738893636.8892</v>
       </c>
       <c r="E908" t="n">
-        <v>10738893638.53947</v>
+        <v>10738893612.2741</v>
       </c>
       <c r="F908" t="n">
         <v>10738893636.8892</v>
       </c>
       <c r="G908" t="n">
-        <v>1.650274276733398</v>
+        <v>-24.6151008605957</v>
       </c>
       <c r="H908" t="n">
-        <v>1.536726531180584e-10</v>
+        <v>-2.292144953930851e-09</v>
       </c>
       <c r="I908" t="n">
         <v>2880</v>
@@ -33180,16 +33180,16 @@
         <v>51983753047.5888</v>
       </c>
       <c r="E909" t="n">
-        <v>51983752211.26623</v>
+        <v>51983752299.93462</v>
       </c>
       <c r="F909" t="n">
         <v>51983753047.5888</v>
       </c>
       <c r="G909" t="n">
-        <v>-836.3225708007812</v>
+        <v>-747.654182434082</v>
       </c>
       <c r="H909" t="n">
-        <v>-1.608815296646945e-08</v>
+        <v>-1.438245872224035e-08</v>
       </c>
       <c r="I909" t="n">
         <v>2880</v>

--- a/notebooks/outputs/building_sector_constraint_evaluation.xlsx
+++ b/notebooks/outputs/building_sector_constraint_evaluation.xlsx
@@ -2188,16 +2188,16 @@
         <v>17483766</v>
       </c>
       <c r="E49" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F49" t="n">
         <v>17483766</v>
       </c>
       <c r="G49" t="n">
-        <v>-15536038</v>
+        <v>-15536034</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8885979142022377</v>
+        <v>-0.8885976854185763</v>
       </c>
       <c r="I49" t="n">
         <v>384</v>
@@ -2224,16 +2224,16 @@
         <v>20440924</v>
       </c>
       <c r="E50" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F50" t="n">
         <v>20440924</v>
       </c>
       <c r="G50" t="n">
-        <v>-18493196</v>
+        <v>-18493192</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.9047142878668303</v>
+        <v>-0.9047140921809601</v>
       </c>
       <c r="I50" t="n">
         <v>384</v>
@@ -2260,16 +2260,16 @@
         <v>23839391</v>
       </c>
       <c r="E51" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F51" t="n">
         <v>23839391</v>
       </c>
       <c r="G51" t="n">
-        <v>-21891663</v>
+        <v>-21891659</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.9182979128955098</v>
+        <v>-0.9182977451059886</v>
       </c>
       <c r="I51" t="n">
         <v>384</v>
@@ -2296,16 +2296,16 @@
         <v>23518958</v>
       </c>
       <c r="E52" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F52" t="n">
         <v>23518958</v>
       </c>
       <c r="G52" t="n">
-        <v>-21571230</v>
+        <v>-21571226</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.9171847664339551</v>
+        <v>-0.9171845963583931</v>
       </c>
       <c r="I52" t="n">
         <v>384</v>
@@ -2332,16 +2332,16 @@
         <v>20471461</v>
       </c>
       <c r="E53" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F53" t="n">
         <v>20471461</v>
       </c>
       <c r="G53" t="n">
-        <v>-18826553</v>
+        <v>-18826552</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.9196487246318179</v>
+        <v>-0.9196486757833259</v>
       </c>
       <c r="I53" t="n">
         <v>96</v>
@@ -5428,16 +5428,16 @@
         <v>1310680</v>
       </c>
       <c r="E139" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F139" t="n">
         <v>1310680</v>
       </c>
       <c r="G139" t="n">
-        <v>637048</v>
+        <v>637052</v>
       </c>
       <c r="H139" t="n">
-        <v>0.4860438856166265</v>
+        <v>0.4860469374675741</v>
       </c>
       <c r="I139" t="n">
         <v>384</v>
@@ -5464,16 +5464,16 @@
         <v>1535401</v>
       </c>
       <c r="E140" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F140" t="n">
         <v>1535401</v>
       </c>
       <c r="G140" t="n">
-        <v>412327</v>
+        <v>412331</v>
       </c>
       <c r="H140" t="n">
-        <v>0.2685467835438429</v>
+        <v>0.268549388726463</v>
       </c>
       <c r="I140" t="n">
         <v>384</v>
@@ -5500,16 +5500,16 @@
         <v>2001685</v>
       </c>
       <c r="E141" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F141" t="n">
         <v>2001685</v>
       </c>
       <c r="G141" t="n">
-        <v>-53957</v>
+        <v>-53953</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.02695578974713804</v>
+        <v>-0.02695379143071962</v>
       </c>
       <c r="I141" t="n">
         <v>384</v>
@@ -5536,16 +5536,16 @@
         <v>1616477</v>
       </c>
       <c r="E142" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F142" t="n">
         <v>1616477</v>
       </c>
       <c r="G142" t="n">
-        <v>331251</v>
+        <v>331255</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2049215670869428</v>
+        <v>0.2049240416040562</v>
       </c>
       <c r="I142" t="n">
         <v>384</v>
@@ -5572,16 +5572,16 @@
         <v>1195648</v>
       </c>
       <c r="E143" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F143" t="n">
         <v>1195648</v>
       </c>
       <c r="G143" t="n">
-        <v>449260</v>
+        <v>449261</v>
       </c>
       <c r="H143" t="n">
-        <v>0.3757460389679906</v>
+        <v>0.3757468753345466</v>
       </c>
       <c r="I143" t="n">
         <v>96</v>
@@ -8668,16 +8668,16 @@
         <v>2038793</v>
       </c>
       <c r="E229" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F229" t="n">
         <v>2038793</v>
       </c>
       <c r="G229" t="n">
-        <v>-91065</v>
+        <v>-91061</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.04466613334458182</v>
+        <v>-0.04466417139945056</v>
       </c>
       <c r="I229" t="n">
         <v>384</v>
@@ -8704,16 +8704,16 @@
         <v>1912967</v>
       </c>
       <c r="E230" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F230" t="n">
         <v>1912967</v>
       </c>
       <c r="G230" t="n">
-        <v>34761</v>
+        <v>34765</v>
       </c>
       <c r="H230" t="n">
-        <v>0.01817124916425636</v>
+        <v>0.01817334015693945</v>
       </c>
       <c r="I230" t="n">
         <v>384</v>
@@ -8740,16 +8740,16 @@
         <v>2013458</v>
       </c>
       <c r="E231" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F231" t="n">
         <v>2013458</v>
       </c>
       <c r="G231" t="n">
-        <v>-65730</v>
+        <v>-65726</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.03264532957727452</v>
+        <v>-0.03264334294532094</v>
       </c>
       <c r="I231" t="n">
         <v>384</v>
@@ -8776,16 +8776,16 @@
         <v>1947743</v>
       </c>
       <c r="E232" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F232" t="n">
         <v>1947743</v>
       </c>
       <c r="G232" t="n">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="H232" t="n">
-        <v>-7.701221362366596e-06</v>
+        <v>-5.64756233240217e-06</v>
       </c>
       <c r="I232" t="n">
         <v>384</v>
@@ -8812,16 +8812,16 @@
         <v>1644908</v>
       </c>
       <c r="E233" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F233" t="n">
         <v>1644908</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>6.07936735671539e-07</v>
       </c>
       <c r="I233" t="n">
         <v>96</v>
@@ -11908,16 +11908,16 @@
         <v>4204538</v>
       </c>
       <c r="E319" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F319" t="n">
         <v>4204538</v>
       </c>
       <c r="G319" t="n">
-        <v>-2256810</v>
+        <v>-2256806</v>
       </c>
       <c r="H319" t="n">
-        <v>-0.5367557624642707</v>
+        <v>-0.5367548111112327</v>
       </c>
       <c r="I319" t="n">
         <v>384</v>
@@ -11944,16 +11944,16 @@
         <v>5486568</v>
       </c>
       <c r="E320" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F320" t="n">
         <v>5486568</v>
       </c>
       <c r="G320" t="n">
-        <v>-3538840</v>
+        <v>-3538836</v>
       </c>
       <c r="H320" t="n">
-        <v>-0.6450006634384191</v>
+        <v>-0.6449999343852113</v>
       </c>
       <c r="I320" t="n">
         <v>384</v>
@@ -11980,16 +11980,16 @@
         <v>6816198</v>
       </c>
       <c r="E321" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F321" t="n">
         <v>6816198</v>
       </c>
       <c r="G321" t="n">
-        <v>-4868470</v>
+        <v>-4868466</v>
       </c>
       <c r="H321" t="n">
-        <v>-0.7142500848713609</v>
+        <v>-0.714249498033948</v>
       </c>
       <c r="I321" t="n">
         <v>384</v>
@@ -12016,16 +12016,16 @@
         <v>6964730</v>
       </c>
       <c r="E322" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F322" t="n">
         <v>6964730</v>
       </c>
       <c r="G322" t="n">
-        <v>-5017002</v>
+        <v>-5016998</v>
       </c>
       <c r="H322" t="n">
-        <v>-0.7203440765112216</v>
+        <v>-0.720343502188886</v>
       </c>
       <c r="I322" t="n">
         <v>384</v>
@@ -12052,16 +12052,16 @@
         <v>5894448</v>
       </c>
       <c r="E323" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F323" t="n">
         <v>5894448</v>
       </c>
       <c r="G323" t="n">
-        <v>-4249540</v>
+        <v>-4249539</v>
       </c>
       <c r="H323" t="n">
-        <v>-0.7209394331750827</v>
+        <v>-0.7209392635239127</v>
       </c>
       <c r="I323" t="n">
         <v>96</v>
@@ -15148,16 +15148,16 @@
         <v>3118121</v>
       </c>
       <c r="E409" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F409" t="n">
         <v>3118121</v>
       </c>
       <c r="G409" t="n">
-        <v>-1170393</v>
+        <v>-1170389</v>
       </c>
       <c r="H409" t="n">
-        <v>-0.3753520148833224</v>
+        <v>-0.3753507320594678</v>
       </c>
       <c r="I409" t="n">
         <v>384</v>
@@ -15184,16 +15184,16 @@
         <v>3422052</v>
       </c>
       <c r="E410" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F410" t="n">
         <v>3422052</v>
       </c>
       <c r="G410" t="n">
-        <v>-1474324</v>
+        <v>-1474320</v>
       </c>
       <c r="H410" t="n">
-        <v>-0.4308303906544962</v>
+        <v>-0.4308292217651865</v>
       </c>
       <c r="I410" t="n">
         <v>384</v>
@@ -15220,16 +15220,16 @@
         <v>4015482</v>
       </c>
       <c r="E411" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F411" t="n">
         <v>4015482</v>
       </c>
       <c r="G411" t="n">
-        <v>-2067754</v>
+        <v>-2067750</v>
       </c>
       <c r="H411" t="n">
-        <v>-0.5149454038145358</v>
+        <v>-0.5149444076701128</v>
       </c>
       <c r="I411" t="n">
         <v>384</v>
@@ -15256,16 +15256,16 @@
         <v>3920377</v>
       </c>
       <c r="E412" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F412" t="n">
         <v>3920377</v>
       </c>
       <c r="G412" t="n">
-        <v>-1972649</v>
+        <v>-1972645</v>
       </c>
       <c r="H412" t="n">
-        <v>-0.5031783933024808</v>
+        <v>-0.5031773729924444</v>
       </c>
       <c r="I412" t="n">
         <v>384</v>
@@ -15292,16 +15292,16 @@
         <v>3626342</v>
       </c>
       <c r="E413" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F413" t="n">
         <v>3626342</v>
       </c>
       <c r="G413" t="n">
-        <v>-1981434</v>
+        <v>-1981433</v>
       </c>
       <c r="H413" t="n">
-        <v>-0.5464002016356979</v>
+        <v>-0.5463999258757172</v>
       </c>
       <c r="I413" t="n">
         <v>96</v>
@@ -18388,16 +18388,16 @@
         <v>1116161</v>
       </c>
       <c r="E499" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F499" t="n">
         <v>1116161</v>
       </c>
       <c r="G499" t="n">
-        <v>831567</v>
+        <v>831571</v>
       </c>
       <c r="H499" t="n">
-        <v>0.745024239334648</v>
+        <v>0.7450278230470335</v>
       </c>
       <c r="I499" t="n">
         <v>384</v>
@@ -18424,16 +18424,16 @@
         <v>1180520</v>
       </c>
       <c r="E500" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F500" t="n">
         <v>1180520</v>
       </c>
       <c r="G500" t="n">
-        <v>767208</v>
+        <v>767212</v>
       </c>
       <c r="H500" t="n">
-        <v>0.6498898790363569</v>
+        <v>0.6498932673736997</v>
       </c>
       <c r="I500" t="n">
         <v>384</v>
@@ -18460,16 +18460,16 @@
         <v>1419030</v>
       </c>
       <c r="E501" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F501" t="n">
         <v>1419030</v>
       </c>
       <c r="G501" t="n">
-        <v>528698</v>
+        <v>528702</v>
       </c>
       <c r="H501" t="n">
-        <v>0.3725770420639451</v>
+        <v>0.3725798608908902</v>
       </c>
       <c r="I501" t="n">
         <v>384</v>
@@ -18496,16 +18496,16 @@
         <v>1346423</v>
       </c>
       <c r="E502" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F502" t="n">
         <v>1346423</v>
       </c>
       <c r="G502" t="n">
-        <v>601305</v>
+        <v>601309</v>
       </c>
       <c r="H502" t="n">
-        <v>0.4465944209212113</v>
+        <v>0.4465973917557855</v>
       </c>
       <c r="I502" t="n">
         <v>384</v>
@@ -18532,16 +18532,16 @@
         <v>1313436</v>
       </c>
       <c r="E503" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F503" t="n">
         <v>1313436</v>
       </c>
       <c r="G503" t="n">
-        <v>331472</v>
+        <v>331473</v>
       </c>
       <c r="H503" t="n">
-        <v>0.2523701192901672</v>
+        <v>0.2523708806519693</v>
       </c>
       <c r="I503" t="n">
         <v>96</v>
@@ -21628,16 +21628,16 @@
         <v>2911838</v>
       </c>
       <c r="E589" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F589" t="n">
         <v>2911838</v>
       </c>
       <c r="G589" t="n">
-        <v>-964110</v>
+        <v>-964106</v>
       </c>
       <c r="H589" t="n">
-        <v>-0.3311001504891412</v>
+        <v>-0.3310987767863459</v>
       </c>
       <c r="I589" t="n">
         <v>384</v>
@@ -21664,16 +21664,16 @@
         <v>3609799</v>
       </c>
       <c r="E590" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F590" t="n">
         <v>3609799</v>
       </c>
       <c r="G590" t="n">
-        <v>-1662071</v>
+        <v>-1662067</v>
       </c>
       <c r="H590" t="n">
-        <v>-0.4604331155280391</v>
+        <v>-0.4604320074331009</v>
       </c>
       <c r="I590" t="n">
         <v>384</v>
@@ -21700,16 +21700,16 @@
         <v>4123047</v>
       </c>
       <c r="E591" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F591" t="n">
         <v>4123047</v>
       </c>
       <c r="G591" t="n">
-        <v>-2175319</v>
+        <v>-2175315</v>
       </c>
       <c r="H591" t="n">
-        <v>-0.5275998551556652</v>
+        <v>-0.5275988849993706</v>
       </c>
       <c r="I591" t="n">
         <v>384</v>
@@ -21736,16 +21736,16 @@
         <v>3786545</v>
       </c>
       <c r="E592" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F592" t="n">
         <v>3786545</v>
       </c>
       <c r="G592" t="n">
-        <v>-1838817</v>
+        <v>-1838813</v>
       </c>
       <c r="H592" t="n">
-        <v>-0.485618684051028</v>
+        <v>-0.4856176276790584</v>
       </c>
       <c r="I592" t="n">
         <v>384</v>
@@ -21772,16 +21772,16 @@
         <v>3139958</v>
       </c>
       <c r="E593" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F593" t="n">
         <v>3139958</v>
       </c>
       <c r="G593" t="n">
-        <v>-1495050</v>
+        <v>-1495049</v>
       </c>
       <c r="H593" t="n">
-        <v>-0.4761369419590963</v>
+        <v>-0.4761366234834988</v>
       </c>
       <c r="I593" t="n">
         <v>96</v>
@@ -24868,16 +24868,16 @@
         <v>1189024</v>
       </c>
       <c r="E679" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F679" t="n">
         <v>1189024</v>
       </c>
       <c r="G679" t="n">
-        <v>758704</v>
+        <v>758708</v>
       </c>
       <c r="H679" t="n">
-        <v>0.6380897273730387</v>
+        <v>0.6380930914767069</v>
       </c>
       <c r="I679" t="n">
         <v>384</v>
@@ -24904,16 +24904,16 @@
         <v>1549032</v>
       </c>
       <c r="E680" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F680" t="n">
         <v>1549032</v>
       </c>
       <c r="G680" t="n">
-        <v>398696</v>
+        <v>398700</v>
       </c>
       <c r="H680" t="n">
-        <v>0.2573839662447258</v>
+        <v>0.2573865485025487</v>
       </c>
       <c r="I680" t="n">
         <v>384</v>
@@ -24940,16 +24940,16 @@
         <v>1639089</v>
       </c>
       <c r="E681" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F681" t="n">
         <v>1639089</v>
       </c>
       <c r="G681" t="n">
-        <v>308639</v>
+        <v>308643</v>
       </c>
       <c r="H681" t="n">
-        <v>0.1882991100544266</v>
+        <v>0.1883015504344182</v>
       </c>
       <c r="I681" t="n">
         <v>384</v>
@@ -24976,16 +24976,16 @@
         <v>1685094</v>
       </c>
       <c r="E682" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F682" t="n">
         <v>1685094</v>
       </c>
       <c r="G682" t="n">
-        <v>262634</v>
+        <v>262638</v>
       </c>
       <c r="H682" t="n">
-        <v>0.155857180667666</v>
+        <v>0.1558595544224833</v>
       </c>
       <c r="I682" t="n">
         <v>384</v>
@@ -25012,16 +25012,16 @@
         <v>1668224</v>
       </c>
       <c r="E683" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F683" t="n">
         <v>1668224</v>
       </c>
       <c r="G683" t="n">
-        <v>-23316</v>
+        <v>-23315</v>
       </c>
       <c r="H683" t="n">
-        <v>-0.01397654032072432</v>
+        <v>-0.01397594088084094</v>
       </c>
       <c r="I683" t="n">
         <v>96</v>
@@ -28108,16 +28108,16 @@
         <v>776138</v>
       </c>
       <c r="E769" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F769" t="n">
         <v>776138</v>
       </c>
       <c r="G769" t="n">
-        <v>1171590</v>
+        <v>1171594</v>
       </c>
       <c r="H769" t="n">
-        <v>1.50951248360472</v>
+        <v>1.509517637327382</v>
       </c>
       <c r="I769" t="n">
         <v>384</v>
@@ -28144,16 +28144,16 @@
         <v>980908</v>
       </c>
       <c r="E770" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F770" t="n">
         <v>980908</v>
       </c>
       <c r="G770" t="n">
-        <v>966820</v>
+        <v>966824</v>
       </c>
       <c r="H770" t="n">
-        <v>0.9856377968168268</v>
+        <v>0.985641874671223</v>
       </c>
       <c r="I770" t="n">
         <v>384</v>
@@ -28180,16 +28180,16 @@
         <v>995797</v>
       </c>
       <c r="E771" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F771" t="n">
         <v>995797</v>
       </c>
       <c r="G771" t="n">
-        <v>951931</v>
+        <v>951935</v>
       </c>
       <c r="H771" t="n">
-        <v>0.9559488530292821</v>
+        <v>0.9559528699122412</v>
       </c>
       <c r="I771" t="n">
         <v>384</v>
@@ -28216,16 +28216,16 @@
         <v>1055709</v>
       </c>
       <c r="E772" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F772" t="n">
         <v>1055709</v>
       </c>
       <c r="G772" t="n">
-        <v>892019</v>
+        <v>892023</v>
       </c>
       <c r="H772" t="n">
-        <v>0.844947802850975</v>
+        <v>0.8449515917738695</v>
       </c>
       <c r="I772" t="n">
         <v>384</v>
@@ -28252,16 +28252,16 @@
         <v>1088268</v>
       </c>
       <c r="E773" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F773" t="n">
         <v>1088268</v>
       </c>
       <c r="G773" t="n">
-        <v>556640</v>
+        <v>556641</v>
       </c>
       <c r="H773" t="n">
-        <v>0.5114916546291906</v>
+        <v>0.5114925735204932</v>
       </c>
       <c r="I773" t="n">
         <v>96</v>
@@ -31348,16 +31348,16 @@
         <v>818473</v>
       </c>
       <c r="E859" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F859" t="n">
         <v>818473</v>
       </c>
       <c r="G859" t="n">
-        <v>1129255</v>
+        <v>1129259</v>
       </c>
       <c r="H859" t="n">
-        <v>1.379709532263129</v>
+        <v>1.379714419412736</v>
       </c>
       <c r="I859" t="n">
         <v>384</v>
@@ -31384,16 +31384,16 @@
         <v>763677</v>
       </c>
       <c r="E860" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F860" t="n">
         <v>763677</v>
       </c>
       <c r="G860" t="n">
-        <v>1184051</v>
+        <v>1184055</v>
       </c>
       <c r="H860" t="n">
-        <v>1.550460469544061</v>
+        <v>1.550465707360573</v>
       </c>
       <c r="I860" t="n">
         <v>384</v>
@@ -31420,16 +31420,16 @@
         <v>815605</v>
       </c>
       <c r="E861" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F861" t="n">
         <v>815605</v>
       </c>
       <c r="G861" t="n">
-        <v>1132123</v>
+        <v>1132127</v>
       </c>
       <c r="H861" t="n">
-        <v>1.388077562055162</v>
+        <v>1.38808246638998</v>
       </c>
       <c r="I861" t="n">
         <v>384</v>
@@ -31456,16 +31456,16 @@
         <v>1195860</v>
       </c>
       <c r="E862" t="n">
-        <v>1947728</v>
+        <v>1947732</v>
       </c>
       <c r="F862" t="n">
         <v>1195860</v>
       </c>
       <c r="G862" t="n">
-        <v>751868</v>
+        <v>751872</v>
       </c>
       <c r="H862" t="n">
-        <v>0.6287257705751509</v>
+        <v>0.6287291154482966</v>
       </c>
       <c r="I862" t="n">
         <v>384</v>
@@ -31492,16 +31492,16 @@
         <v>900229</v>
       </c>
       <c r="E863" t="n">
-        <v>1644908</v>
+        <v>1644909</v>
       </c>
       <c r="F863" t="n">
         <v>900229</v>
       </c>
       <c r="G863" t="n">
-        <v>744679</v>
+        <v>744680</v>
       </c>
       <c r="H863" t="n">
-        <v>0.8272106319614232</v>
+        <v>0.8272117427898902</v>
       </c>
       <c r="I863" t="n">
         <v>96</v>
@@ -32940,16 +32940,16 @@
         <v>19720127178.55555</v>
       </c>
       <c r="E903" t="n">
-        <v>19720127192.18081</v>
+        <v>19720127185.25605</v>
       </c>
       <c r="F903" t="n">
         <v>19720127178.55555</v>
       </c>
       <c r="G903" t="n">
-        <v>13.62525177001953</v>
+        <v>6.70050048828125</v>
       </c>
       <c r="H903" t="n">
-        <v>6.909312321695455e-10</v>
+        <v>3.397797807089013e-10</v>
       </c>
       <c r="I903" t="n">
         <v>2880</v>
@@ -32980,16 +32980,16 @@
         <v>9715263599.055555</v>
       </c>
       <c r="E904" t="n">
-        <v>9715263607.113047</v>
+        <v>9715263598.284626</v>
       </c>
       <c r="F904" t="n">
         <v>9715263599.055555</v>
       </c>
       <c r="G904" t="n">
-        <v>8.057491302490234</v>
+        <v>-0.7709293365478516</v>
       </c>
       <c r="H904" t="n">
-        <v>8.293641464626367e-10</v>
+        <v>-7.935238490315337e-11</v>
       </c>
       <c r="I904" t="n">
         <v>2880</v>
@@ -33020,16 +33020,16 @@
         <v>10854992261.36111</v>
       </c>
       <c r="E905" t="n">
-        <v>10854992269.14477</v>
+        <v>10854992254.54099</v>
       </c>
       <c r="F905" t="n">
         <v>10854992261.36111</v>
       </c>
       <c r="G905" t="n">
-        <v>7.783658981323242</v>
+        <v>-6.82011604309082</v>
       </c>
       <c r="H905" t="n">
-        <v>7.170579945072432e-10</v>
+        <v>-6.282930359487556e-10</v>
       </c>
       <c r="I905" t="n">
         <v>2880</v>
@@ -33100,16 +33100,16 @@
         <v>2204916009.7266</v>
       </c>
       <c r="E907" t="n">
-        <v>9314434548.234623</v>
+        <v>9314434518.80929</v>
       </c>
       <c r="F907" t="n">
         <v>2204916009.7266</v>
       </c>
       <c r="G907" t="n">
-        <v>7109518538.508023</v>
+        <v>7109518509.08269</v>
       </c>
       <c r="H907" t="n">
-        <v>3.224394265879349</v>
+        <v>3.224394252534019</v>
       </c>
       <c r="I907" t="n">
         <v>1440</v>
@@ -33140,16 +33140,16 @@
         <v>10738893636.8892</v>
       </c>
       <c r="E908" t="n">
-        <v>10738893845.3769</v>
+        <v>10738893813.42393</v>
       </c>
       <c r="F908" t="n">
         <v>10738893636.8892</v>
       </c>
       <c r="G908" t="n">
-        <v>208.4876976013184</v>
+        <v>176.5347290039062</v>
       </c>
       <c r="H908" t="n">
-        <v>1.94142622742013e-08</v>
+        <v>1.643881902298495e-08</v>
       </c>
       <c r="I908" t="n">
         <v>2880</v>
@@ -33180,16 +33180,16 @@
         <v>51983753047.5888</v>
       </c>
       <c r="E909" t="n">
-        <v>51983753640.6458</v>
+        <v>51983753576.42473</v>
       </c>
       <c r="F909" t="n">
         <v>51983753047.5888</v>
       </c>
       <c r="G909" t="n">
-        <v>593.056999206543</v>
+        <v>528.8359298706055</v>
       </c>
       <c r="H909" t="n">
-        <v>1.140850678217915e-08</v>
+        <v>1.017310022588173e-08</v>
       </c>
       <c r="I909" t="n">
         <v>2880</v>
